--- a/daily_matches/job_matches_2026-04-23.xlsx
+++ b/daily_matches/job_matches_2026-04-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.1</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, OpenCV, Docker, Kubernetes, CI/CD, Jenkins</t>
+          <t>Data Scientist, RAG, BigQuery, Dataflow, Docker, Kubernetes, CI/CD, Git, BigQuery, Kafka</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,67 +496,67 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e288d00b33f48efe</t>
+          <t>https://www.indeed.com/viewjob?jk=9a75bae8fe6b588f</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>UCLA Health</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, TensorFlow, Keras, Databricks, Tableau, Power BI, Matplotlib, Python</t>
+          <t>Data Scientist, RAG, BigQuery, Dataflow, Docker, Kubernetes, CI/CD, Git, BigQuery, Kafka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=547597dde0ad4f1d</t>
+          <t>https://www.indeed.com/viewjob?jk=be5d882b0154cb62</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pre-Sales Engineer (Data &amp; Analytics)</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Redshift, BigQuery, Synapse, Snowflake, Databricks, BigQuery, Redshift, Python, SQL, R</t>
+          <t>TensorFlow, PyTorch, AWS SageMaker, S3, EC2, Glue, Redshift, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c940790b1550a5b</t>
+          <t>https://www.indeed.com/viewjob?jk=eec716db1d652f56</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Applied AI ML Engineer Associate</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Open Access Technology International</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, CI/CD, Jenkins, Terraform, Git, Python, R, Java</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, Git, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,77 +601,812 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abdfa0cbe4dd9220</t>
+          <t>https://www.indeed.com/viewjob?jk=d8af5a5163d243f7</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, Git, Kafka, MongoDB, SQL, R, Java, Scala</t>
+          <t>Generative AI, RAG, S3, EC2, Glue, Docker, Kubernetes, CI/CD, Jenkins, Git</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d93fae7a16728c65</t>
+          <t>https://www.indeed.com/viewjob?jk=fbdcf2158c6b2d0d</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data Engineering</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>GitHub</t>
+          <t>Renesas</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Kafka</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f4c91903cae2e080</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Hugging Face, TensorFlow, PyTorch, Kubernetes, Kafka, Python</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=82af2431009c0a66</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, TensorFlow, PyTorch, Keras, Docker, Kubernetes, CI/CD, Hadoop</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5b0780a9fb0dbc39</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>AI Integration Engineer (Java + AI)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>RAG, S3, Docker, Kubernetes, CI/CD, Git, Kafka, NoSQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6bd882abe2f239e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Java Software Engineer</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Gemini, Docker, Kubernetes, CI/CD, Jenkins, Terraform, MySQL, NoSQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5f84e68d5415404a</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Data Engineer (AIA)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Data Lake, Docker, Kubernetes, CI/CD, Git, Snowflake, Databricks, Python</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e8f49ea5746dd899</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>DevOps/AI Ops Administrator</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Data Lake, Kinesis, CI/CD, Databricks, PySpark, Kafka, SQL, R</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=41f5f841b3bf67ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Software Engineer, Data Platform</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Redshift, BigQuery, Terraform, Snowflake, BigQuery, Redshift, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=45e12b77b9565199</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>AI Integration Engineer (Java + AI)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Docker, CI/CD, Jenkins, Terraform, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=af37d87136cf35b5</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>AI Integration Engineer (Java + AI)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, Kafka, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ed9567131d623dc4</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Hugging Face, TensorFlow, PyTorch, spaCy, NLTK, Git, Kafka, Python</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4143819d9df89d0c</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Infrastructure Software Engineer I</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Jack Henry &amp; Associates</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Springfield, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Dataflow, Docker, Kubernetes, Terraform, Git, BigQuery, MongoDB, Python</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8fb7a554510cc0c6</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Senior Specialist - Architecture (AI Engineer with Codex Exp.)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>LTIMindtree</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Berkeley Heights, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Docker, Kubernetes, Kafka, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=65c00c71c8e6928e</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Sr Software Engineer (QA)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Think IT Technologies</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=00f170353ec794e4</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>AI Integration Engineer (Java + AI)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f3f1c6bd2677948e</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Varteq</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
           <t>Remote, US USA</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, TensorFlow, PyTorch, XGBoost, AWS SageMaker, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=224803835b2ef8a5</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Senior Performance Engineer (Cloud &amp; Distributed Systems)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Infenox Technologies</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>California City, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
         <v>10</v>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, CI/CD, Git, MySQL, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, NoSQL, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=62c6772efd79dde7</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Data Scientist, TensorFlow, PyTorch, Git, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9e2ecaf92624beab</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Data Scientist, TensorFlow, PyTorch, MLflow, Databricks, Hadoop, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3be00621dd9bb1de</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Engineer, AI/ML Operations</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Comcast</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Kubernetes, Git, Kafka, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
         <is>
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0b572d50339a701b</t>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b0fa64807b3988f4</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Senior Cloud Software Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Twilio</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RAG, S3, Athena, Terraform, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=222e043b551a3e70</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Cloud Software Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Lincoln Electric</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, MySQL, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5a01aeaaa6173e69</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-23.xlsx
+++ b/daily_matches/job_matches_2026-04-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Java AI / ML Integration Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Dataflow, Docker, Kubernetes, CI/CD, Git, BigQuery, Kafka</t>
+          <t>AI Engineer, Data Scientist, RAG, S3, Glue, Redshift, CI/CD, Git, Databricks, Redshift</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a75bae8fe6b588f</t>
+          <t>https://www.indeed.com/viewjob?jk=ebc27b8ad561d2ae</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer II - AI Solutions</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Dataflow, Docker, Kubernetes, CI/CD, Git, BigQuery, Kafka</t>
+          <t>Data Scientist, LangChain, RAG, TensorFlow, PyTorch, Keras, Docker, Kubernetes, CI/CD, Databricks</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,14 +531,14 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be5d882b0154cb62</t>
+          <t>https://www.indeed.com/viewjob?jk=488caabc0de3fad8</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>TensorFlow, PyTorch, AWS SageMaker, S3, EC2, Glue, Redshift, Docker, Kubernetes, CI/CD</t>
+          <t>Data Scientist, RAG, Pinecone, Docker, Kubernetes, Kafka, Hadoop, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eec716db1d652f56</t>
+          <t>https://www.indeed.com/viewjob?jk=4ac82b1c79d8bff3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>AI Engineer/ML Engineer - Senior Developers - AI Training - El Paso, US</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Open Access Technology International</t>
+          <t>Prolific Academic Ltd</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>El Paso, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, Git, Python</t>
+          <t>AI Engineer, Machine Learning Engineer, LangChain, RAG, Hugging Face, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Keras</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8af5a5163d243f7</t>
+          <t>https://www.indeed.com/viewjob?jk=7ee5e02fe5245ae7</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>AI Engineer/ML Engineer - Senior Developers - AI Training - USA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Prolific Academic Ltd</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, S3, EC2, Glue, Docker, Kubernetes, CI/CD, Jenkins, Git</t>
+          <t>AI Engineer, Machine Learning Engineer, LangChain, RAG, Hugging Face, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Keras</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbdcf2158c6b2d0d</t>
+          <t>https://www.indeed.com/viewjob?jk=790a59a47a1f6020</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>AI Engineer/ML Engineer - Senior Developers - AI Training - San Jose, USA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Renesas</t>
+          <t>Prolific Academic Ltd</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,42 +661,42 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Kafka</t>
+          <t>AI Engineer, Machine Learning Engineer, LangChain, RAG, Hugging Face, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Keras</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4c91903cae2e080</t>
+          <t>https://www.indeed.com/viewjob?jk=e62562f3b244d0ce</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>AI Engineer/ML Engineer - Senior Developers - AI Training - Nashville, US</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Prolific Academic Ltd</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Hugging Face, TensorFlow, PyTorch, Kubernetes, Kafka, Python</t>
+          <t>AI Engineer, Machine Learning Engineer, LangChain, RAG, Hugging Face, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Keras</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82af2431009c0a66</t>
+          <t>https://www.indeed.com/viewjob?jk=76af632cea31ab2b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>AI Engineer/ML Engineer - Senior Developers - AI Training - San Diego, USA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Prolific Academic Ltd</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, TensorFlow, PyTorch, Keras, Docker, Kubernetes, CI/CD, Hadoop</t>
+          <t>AI Engineer, Machine Learning Engineer, LangChain, RAG, Hugging Face, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Keras</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b0780a9fb0dbc39</t>
+          <t>https://www.indeed.com/viewjob?jk=5fcdab4f5c0b6cc7</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>AI Engineer/ML Engineer - Senior Developers - AI Training - Boston, US</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Prolific Academic Ltd</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, Kubernetes, CI/CD, Git, Kafka, NoSQL, Python, SQL</t>
+          <t>AI Engineer, Machine Learning Engineer, LangChain, RAG, Hugging Face, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Keras</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bd882abe2f239e8</t>
+          <t>https://www.indeed.com/viewjob?jk=6bdf8039d5fa5724</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Java Software Engineer</t>
+          <t>AI Engineer/ML Engineer - Senior Developers - AI Training - Portland, US</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Prolific Academic Ltd</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gemini, Docker, Kubernetes, CI/CD, Jenkins, Terraform, MySQL, NoSQL, Python, SQL</t>
+          <t>AI Engineer, Machine Learning Engineer, LangChain, RAG, Hugging Face, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Keras</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,67 +811,67 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f84e68d5415404a</t>
+          <t>https://www.indeed.com/viewjob?jk=bc189ab44d785f92</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer (AIA)</t>
+          <t>AI Engineer/ML Engineer - Senior Developers - AI Training - Austin, US</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Prolific Academic Ltd</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, Docker, Kubernetes, CI/CD, Git, Snowflake, Databricks, Python</t>
+          <t>AI Engineer, Machine Learning Engineer, LangChain, RAG, Hugging Face, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Keras</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8f49ea5746dd899</t>
+          <t>https://www.indeed.com/viewjob?jk=37962b2ea88738e5</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>AI Engineer/ML Engineer - Senior Developers - AI Training - San Francisco, US</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Prolific Academic Ltd</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, Kinesis, CI/CD, Databricks, PySpark, Kafka, SQL, R</t>
+          <t>AI Engineer, Machine Learning Engineer, LangChain, RAG, Hugging Face, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Keras</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,67 +881,67 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41f5f841b3bf67ad</t>
+          <t>https://www.indeed.com/viewjob?jk=cf776a2c42f92f1f</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Platform</t>
+          <t>AI Engineer/ML Engineer - Senior Developers - AI Training - Dallas, USA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ramp</t>
+          <t>Prolific Academic Ltd</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Redshift, BigQuery, Terraform, Snowflake, BigQuery, Redshift, Python, SQL</t>
+          <t>AI Engineer, Machine Learning Engineer, LangChain, RAG, Hugging Face, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Keras</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45e12b77b9565199</t>
+          <t>https://www.indeed.com/viewjob?jk=5a3c18ea18ed8a89</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>AI Engineer/ML Engineer - Senior Developers - AI Training - Washington DC, US</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Prolific Academic Ltd</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, CI/CD, Jenkins, Terraform, Git, Python, R, Java</t>
+          <t>AI Engineer, Machine Learning Engineer, LangChain, RAG, Hugging Face, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Keras</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af37d87136cf35b5</t>
+          <t>https://www.indeed.com/viewjob?jk=ee760ba14547ca1a</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>AI Engineer/ML Engineer - Senior Developers - AI Training - Indianapolis, US</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Prolific Academic Ltd</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, Kafka, R, Java, Scala</t>
+          <t>AI Engineer, Machine Learning Engineer, LangChain, RAG, Hugging Face, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Keras</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed9567131d623dc4</t>
+          <t>https://www.indeed.com/viewjob?jk=a527b523470b7476</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>AI Engineer/ML Engineer - Senior Developers - AI Training - Fort Worth, US</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Prolific Academic Ltd</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Hugging Face, TensorFlow, PyTorch, spaCy, NLTK, Git, Kafka, Python</t>
+          <t>AI Engineer, Machine Learning Engineer, LangChain, RAG, Hugging Face, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Keras</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,67 +1021,67 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4143819d9df89d0c</t>
+          <t>https://www.indeed.com/viewjob?jk=d155dd4c97bdd5bd</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Infrastructure Software Engineer I</t>
+          <t>AI Engineer/ML Engineer - Senior Developers - AI Training - Charlotte, US</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Jack Henry &amp; Associates</t>
+          <t>Prolific Academic Ltd</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Dataflow, Docker, Kubernetes, Terraform, Git, BigQuery, MongoDB, Python</t>
+          <t>AI Engineer, Machine Learning Engineer, LangChain, RAG, Hugging Face, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Keras</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fb7a554510cc0c6</t>
+          <t>https://www.indeed.com/viewjob?jk=f59430ed8304b82d</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Specialist - Architecture (AI Engineer with Codex Exp.)</t>
+          <t>AI Engineer/ML Engineer - Senior Developers - AI Training - Las Vegas, US</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Prolific Academic Ltd</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Docker, Kubernetes, Kafka, Python, SQL, R, Java</t>
+          <t>AI Engineer, Machine Learning Engineer, LangChain, RAG, Hugging Face, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Keras</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65c00c71c8e6928e</t>
+          <t>https://www.indeed.com/viewjob?jk=9fbdccb3a5b1c1a0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr Software Engineer (QA)</t>
+          <t>AI Engineer/ML Engineer - Senior Developers - AI Training - Columbus, US</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Think IT Technologies</t>
+          <t>Prolific Academic Ltd</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R, Java, Scala</t>
+          <t>AI Engineer, Machine Learning Engineer, LangChain, RAG, Hugging Face, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Keras</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00f170353ec794e4</t>
+          <t>https://www.indeed.com/viewjob?jk=3e26bc455c87e187</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>AI Engineer/ML Engineer - Senior Developers - AI Training - USA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Prolific Academic Ltd</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala, Optimization</t>
+          <t>AI Engineer, Machine Learning Engineer, LangChain, RAG, Hugging Face, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Keras</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3f1c6bd2677948e</t>
+          <t>https://www.indeed.com/viewjob?jk=661cbe637c6b52c1</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>AI Engineer/ML Engineer - Senior Developers - AI Training - Denver, US</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Varteq</t>
+          <t>Prolific Academic Ltd</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, TensorFlow, PyTorch, XGBoost, AWS SageMaker, Git, Python, R, Scala, Optimization</t>
+          <t>AI Engineer, Machine Learning Engineer, LangChain, RAG, Hugging Face, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Keras</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=224803835b2ef8a5</t>
+          <t>https://www.indeed.com/viewjob?jk=9888208b6787350b</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Performance Engineer (Cloud &amp; Distributed Systems)</t>
+          <t>AI Engineer/ML Engineer - Senior Developers - AI Training - Jacksonville, US</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Infenox Technologies</t>
+          <t>Prolific Academic Ltd</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>California City, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>10</v>
+        <v>15.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, NoSQL, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>AI Engineer, Machine Learning Engineer, LangChain, RAG, Hugging Face, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Keras</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62c6772efd79dde7</t>
+          <t>https://www.indeed.com/viewjob?jk=51d1e813bb507510</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>AI Engineer/ML Engineer - Senior Developers - AI Training - USA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Prolific Academic Ltd</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>10</v>
+        <v>15.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Data Scientist, TensorFlow, PyTorch, Git, Databricks, Python, SQL, R, Scala</t>
+          <t>AI Engineer, Machine Learning Engineer, LangChain, RAG, Hugging Face, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Keras</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e2ecaf92624beab</t>
+          <t>https://www.indeed.com/viewjob?jk=9f07a6c2755c5abe</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>AI Engineer/ML Engineer - Senior Developers - AI Training - Oklahoma City, US</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Prolific Academic Ltd</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>10</v>
+        <v>15.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Data Scientist, TensorFlow, PyTorch, MLflow, Databricks, Hadoop, Python, R, Java</t>
+          <t>AI Engineer, Machine Learning Engineer, LangChain, RAG, Hugging Face, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Keras</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,112 +1301,812 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3be00621dd9bb1de</t>
+          <t>https://www.indeed.com/viewjob?jk=25c966d26f008c38</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Engineer, AI/ML Operations</t>
+          <t>AI Engineer/ML Engineer - Senior Developers - AI Training - USA</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Prolific Academic Ltd</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>10</v>
+        <v>15.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, Git, Kafka, Python, R, Scala, Optimization</t>
+          <t>AI Engineer, Machine Learning Engineer, LangChain, RAG, Hugging Face, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Keras</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0fa64807b3988f4</t>
+          <t>https://www.indeed.com/viewjob?jk=1eab0cc03baf3bca</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Cloud Software Engineer</t>
+          <t>AI Engineer/ML Engineer - Senior Developers - AI Training - Seattle, US</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Prolific Academic Ltd</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>10</v>
+        <v>15.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RAG, S3, Athena, Terraform, Python, R, Java, Scala, Optimization</t>
+          <t>AI Engineer, Machine Learning Engineer, LangChain, RAG, Hugging Face, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Keras</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=222e043b551a3e70</t>
+          <t>https://www.indeed.com/viewjob?jk=1962f398a0df9f05</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Cloud Software Engineer</t>
+          <t>AI Engineer/ML Engineer - Senior Developers - AI Training - USA</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Lincoln Electric</t>
+          <t>Prolific Academic Ltd</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, LangChain, RAG, Hugging Face, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Keras</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=49fb1cf79e3db24b</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>AI Engineer/ML Engineer - Senior Developers - AI Training - USA</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Prolific Academic Ltd</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, LangChain, RAG, Hugging Face, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Keras</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6bf77ad314992b5e</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>AI Engineer/ML Engineer - Senior Developers - AI Training - USA</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Prolific Academic Ltd</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, LangChain, RAG, Hugging Face, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Keras</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=46f819bdb2c47296</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Data Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Apptronik</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, RAG, Docker, Kubernetes, Terraform, Kafka, PostgreSQL, NoSQL, Python</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6c8a6b6744212463</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Walker &amp; Dunlop</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RAG, FastAPI, Docker, Kubernetes, CI/CD, Git, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8bcd1b8688c7b138</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>AI Integration Engineer (Java + AI)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Jenkins, Git, Snowflake, Kafka, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=941ac241f296e056</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Cloud AI Application Administrator</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>LangChain, S3, Athena, Redshift, CI/CD, Terraform, Redshift, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c0a2cb39a283363f</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, AI Products</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Cambio AI Inc.</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, CI/CD, Git, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9753947e908b0612</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Empirx Health</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Data Lake, CI/CD, Git, Databricks, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=df86a0c4dd78dfc1</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence (AI) Engineer</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Techsur Solutions</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Reston, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, TensorFlow, PyTorch, Keras, Docker, Kubernetes, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6e8056a17f7ff666</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>AI/ML Engineer</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Pandit View Software LLC</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Hadoop, Dask, Python, R</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7debbaf81a46af18</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Software Engineer Supervisor (System Admin)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>HR1Systems, LLC</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>RAG, MLflow, Docker, Kubernetes, Git, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dce8e726beb67f2b</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>AI Retrieval &amp; Relevance Engineer (RAG / Hybrid Search)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>iBusiness Funding</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Fort Lauderdale, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>RAG, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3fc1a2625b55a88f</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Advanced Analytics &amp; Research Specialist</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Great American Insurance Group</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, TensorFlow, PyTorch, Docker, Kubernetes, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=73d866179fff1a7c</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Axios</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, Git, MySQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=64eb815865832221</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Generative AI Engineer</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Vforce Infotech</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Edison, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=55b584bb5037d0cf</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Lyft Business</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Lyft</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
         <v>10</v>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, CI/CD, MySQL, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5a01aeaaa6173e69</t>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, LangChain, RAG, Prompt Engineering, AWS SageMaker, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d0db937d0a9bb8d5</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Lyft Business</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Lyft</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>10</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, LangChain, RAG, Prompt Engineering, AWS SageMaker, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ffee6de875ad7a49</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Software Engineer I</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Empirx Health</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>10</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Data Lake, CI/CD, Git, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7a3842b879e99023</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Warranty Data Analyst / Data Scientist</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Stellantis</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Auburn Hills, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>10</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Data Scientist, Snowflake, Databricks, PySpark, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=abdbd26974d27e06</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>FIGS</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Santa Monica, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>10</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>RAG, Cortex, Snowflake, Databricks, Tableau, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cd96ce3b549a228b</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-23.xlsx
+++ b/daily_matches/job_matches_2026-04-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Software Engineer</t>
+          <t>Analytics, Full-Stack Engineer (Agency Temp)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NitinX</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, PostgreSQL</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Cortex, CI/CD, Snowflake, Databricks, PySpark, Power BI</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20cbaecb52ef1e29</t>
+          <t>https://www.indeed.com/viewjob?jk=78330a31d3de60c8</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Veridic Solutions</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Redford, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, OpenCV, BigQuery, Docker, Kubernetes, CI/CD, Git</t>
+          <t>Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, FastAPI, CI/CD, Jenkins, Terraform, Git</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e7e00de56aa8558</t>
+          <t>https://www.indeed.com/viewjob?jk=000191587a0bd612</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Summer 2026 Inten - IT MFG Architecture</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>WD</t>
+          <t>Books-A-Million</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Prompt Engineering, TensorFlow, PyTorch, Git, Tableau, Power BI, Python, SQL</t>
+          <t>RAG, S3, Redshift, BigQuery, Data Lake, Git, BigQuery, Redshift, Python, SQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b9adae7c22d48ad</t>
+          <t>https://www.indeed.com/viewjob?jk=dd3b3b5af84f7f50</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Investment Compliance Engineer</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Apollo</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, NoSQL, Python</t>
+          <t>AI Engineer, RAG, S3, Glue, Athena, Data Lake, CI/CD, Git, Quicksight, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef318708de3b36bf</t>
+          <t>https://www.indeed.com/viewjob?jk=c1c509a2c5d165cf</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer - Market Solutions Portfolio</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Wellmark Blue Cross and Blue Shield</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>S3, Glue, Redshift, CI/CD, Git, Redshift, Python, SQL, R, Scala</t>
+          <t>AI Engineer, RAG, S3, Glue, Athena, Data Lake, CI/CD, Git, Quicksight, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01af0741f779b099</t>
+          <t>https://www.indeed.com/viewjob?jk=16029f18260b23a7</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, AI</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Synack</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Kafka, NoSQL, Python, SQL, R, Scala, Optimization</t>
+          <t>AI Engineer, RAG, S3, Glue, Athena, Data Lake, CI/CD, Git, Quicksight, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39dcb6f54c0fd8b6</t>
+          <t>https://www.indeed.com/viewjob?jk=585c6ab4414e23c8</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Warranty Data Analyst / Data Scientist</t>
+          <t>Asset &amp; Wealth Management - Software Engineer - Associate - Dallas</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Snowflake, Databricks, PySpark, Power BI, Python, SQL, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, MongoDB, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82beb43a57ee8ec5</t>
+          <t>https://www.indeed.com/viewjob?jk=0b0170a8c239abcc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Healthcare Data Analyst - Jefferson Health Plan</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ATPCO</t>
+          <t>Thomas Jefferson University &amp; Jefferson Health</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>RAG, BigQuery, Synapse, Snowflake, Databricks, BigQuery, Tableau, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e194a6715c71f27d</t>
+          <t>https://www.indeed.com/viewjob?jk=99fb925c10b50b67</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IT AI Development Intern</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Amphenol CIT</t>
+          <t>Electrosoft</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Saint Augustine, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Generative AI, Copilot, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Git, Python, R, Java</t>
+          <t>Data Scientist, S3, Glue, Redshift, Synapse, Databricks, Redshift, Tableau, Power BI, Python</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e27beb6ed5bbd08b</t>
+          <t>https://www.indeed.com/viewjob?jk=e74838c91725d1c0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Supply Chain Data Analyst</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Fortune Brands Innovations</t>
+          <t>Electrosoft</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Git, Snowflake, Tableau, Power BI, Python, SQL, R, Optimization</t>
+          <t>Data Scientist, S3, Glue, Redshift, Synapse, Databricks, Redshift, Tableau, Power BI, Python</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,42 +811,672 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c6aeb0985410b78</t>
+          <t>https://www.indeed.com/viewjob?jk=85b344a8502c5244</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Consumer Behavior Modeler II</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>Scan.com</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>RAG, Cortex, BigQuery, CI/CD, Git, Snowflake, BigQuery, Tableau, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4a64073277b7a7d6</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Data Analyst</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Scan.com</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RAG, Cortex, BigQuery, CI/CD, Git, Snowflake, BigQuery, Tableau, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4412f02b8aa924fa</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Incentive Offers</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Metropolis</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, Snowflake, PostgreSQL, MySQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c447b651ee800dde</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>DEVSECOPS(Openshift/Harness/Github Actions)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Intone Networks</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
           <t>Charlotte, NC, US USA</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D15" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>CI/CD, Jenkins, GitHub Actions, Git, Kafka, MongoDB, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=533d36ca5b4598d9</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Sr. Marketing Data Analyst</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>WebstaurantStore</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Lititz, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Data Lake, BigQuery, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ffd7a5644f82136e</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Sr. Business Intelligence Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Crane Worldwide Logistics</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Power BI, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ca7e276fb38eb9c1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Data Infrastructure &amp; AI</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>fullstory</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Git, Snowflake, Databricks, BigQuery, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6120c45b70e1da1f</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Senior Site Reliability Engineer - Moneylion</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Gen Digital Inc.</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Tempe, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=72184d7f26e035eb</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Senior Site Reliability Engineer - Moneylion</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Gen Digital Inc.</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dafd0312251318c4</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Senior Data Ops Engineer (contract)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Wells Fargo</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Prompt Engineering, BigQuery, Data Lake, BigQuery, PySpark, Kafka, Python, R</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d1e21d61725d3203</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Epiq</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Docker, Kubernetes, Terraform, PostgreSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2384b69265cb7bcf</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>IT AI Development Intern</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Amphenol CIT</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Saint Augustine, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Generative AI, Copilot, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4304f11c3c46c971</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Sr. Data Scientist</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ResultStack</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>SC, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Data Scientist, Docker, CI/CD, Git, Tableau, Power BI, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=383dabd5b047d81f</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Sr. Data Scientist</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ResultStack</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Data Scientist, Docker, CI/CD, Git, Tableau, Power BI, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4b52adf19e2ee5eb</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Sr. Data Scientist</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ResultStack</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Data Scientist, Docker, CI/CD, Git, Tableau, Power BI, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4a7add81c0661915</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Software Developer - Information Governance</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Epiq</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Overland Park, KS, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
         <v>10</v>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Generative AI, LangChain, RAG, Prompt Engineering, FastAPI, Hadoop, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=69d0ad2b6781b0bf</t>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, GitHub Actions, Git, NoSQL, Power BI, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=88087b3c950df52e</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Data Engineering</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Chime</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RAG, Glue, Redshift, Snowflake, Redshift, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3c132b6601f3c0c7</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>AI Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>COLORADO SCHOOL OF MINES</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Golden, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Gemini, Copilot, Prompt Engineering, Git, R</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=642b8ac64c59f946</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Applied AI Engineer, Silicon Co-Design Group, New College Grad 2026</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Santa Clara, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, TensorFlow, PyTorch, CI/CD, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a3fa64adf9400cb4</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-23.xlsx
+++ b/daily_matches/job_matches_2026-04-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Analytics, Full-Stack Engineer (Agency Temp)</t>
+          <t>Software Engineer- Agentic AI &amp; DevOps (Remote)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SCAN Health Plan</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Cortex, CI/CD, Snowflake, Databricks, PySpark, Power BI</t>
+          <t>LangChain, RAG, Prompt Engineering, Dataflow, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78330a31d3de60c8</t>
+          <t>https://www.indeed.com/viewjob?jk=983cd52a5aa42147</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Senior Cloud &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Veridic Solutions</t>
+          <t>Prologis</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, FastAPI, CI/CD, Jenkins, Terraform, Git</t>
+          <t>AI Engineer, LangChain, RAG, Copilot, S3, EC2, CI/CD, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=000191587a0bd612</t>
+          <t>https://www.indeed.com/viewjob?jk=f0666935e030509b</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Books-A-Million</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, S3, Redshift, BigQuery, Data Lake, Git, BigQuery, Redshift, Python, SQL</t>
+          <t>AI Engineer, Generative AI, Prompt Engineering, TensorFlow, PyTorch, AWS SageMaker, S3, EC2, Python, R</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd3b3b5af84f7f50</t>
+          <t>https://www.indeed.com/viewjob?jk=be8cff6ac33c1fed</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>PySpark Software Engineer III - Python/Java/SQL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, S3, Glue, Athena, Data Lake, CI/CD, Git, Quicksight, Python</t>
+          <t>LangChain, RAG, CI/CD, Databricks, PySpark, Kafka, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1c509a2c5d165cf</t>
+          <t>https://www.indeed.com/viewjob?jk=78bdd7b5a804850b</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Analytics &amp; BI Spclst 3 or Sr</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>MidAmerican Energy</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, S3, Glue, Athena, Data Lake, CI/CD, Git, Quicksight, Python</t>
+          <t>Data Scientist, RAG, Data Lake, CI/CD, Snowflake, Databricks, PySpark, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16029f18260b23a7</t>
+          <t>https://www.indeed.com/viewjob?jk=bb9c48f1459d1dac</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Software Engineer, Cash App - Controls</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, S3, Glue, Athena, Data Lake, CI/CD, Git, Quicksight, Python</t>
+          <t>RAG, Copilot, Kubernetes, Git, Kafka, MySQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=585c6ab4414e23c8</t>
+          <t>https://www.indeed.com/viewjob?jk=409c4995785aa0be</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management - Software Engineer - Associate - Dallas</t>
+          <t>Software Engineer, Cash App - Controls</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Kafka, MongoDB, NoSQL, SQL, R</t>
+          <t>RAG, Copilot, Kubernetes, Git, Kafka, MySQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b0170a8c239abcc</t>
+          <t>https://www.indeed.com/viewjob?jk=007cd474ad8de3fe</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Healthcare Data Analyst - Jefferson Health Plan</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Thomas Jefferson University &amp; Jefferson Health</t>
+          <t>Halvik</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Synapse, Snowflake, Databricks, BigQuery, Tableau, Power BI, Python, SQL</t>
+          <t>RAG, S3, Redshift, Data Lake, CI/CD, Git, Databricks, Redshift, Tableau, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99fb925c10b50b67</t>
+          <t>https://www.indeed.com/viewjob?jk=341490c7d903c2bd</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Engineer I, Observability</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Electrosoft</t>
+          <t>DigitalOcean</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, S3, Glue, Redshift, Synapse, Databricks, Redshift, Tableau, Power BI, Python</t>
+          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Kafka, R, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e74838c91725d1c0</t>
+          <t>https://www.indeed.com/viewjob?jk=b21e4fdf2d48c700</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Electrosoft</t>
+          <t>Westinghouse Electric Company, LLC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cranberry Township, PA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, S3, Glue, Redshift, Synapse, Databricks, Redshift, Tableau, Power BI, Python</t>
+          <t>Data Scientist, RAG, Git, Databricks, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85b344a8502c5244</t>
+          <t>https://www.indeed.com/viewjob?jk=1165aee444b7a2a9</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>AI Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Scan.com</t>
+          <t>UpSmith</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Cortex, BigQuery, CI/CD, Git, Snowflake, BigQuery, Tableau, Python, SQL</t>
+          <t>RAG, S3, Kubernetes, AKS, PostgreSQL, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a64073277b7a7d6</t>
+          <t>https://www.indeed.com/viewjob?jk=20be00ff86a10751</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Scan.com</t>
+          <t>Bilt Rewards</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Cortex, BigQuery, CI/CD, Git, Snowflake, BigQuery, Tableau, Python, SQL</t>
+          <t>RAG, Copilot, CI/CD, Git, NoSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4412f02b8aa924fa</t>
+          <t>https://www.indeed.com/viewjob?jk=eb40f3e808c5444b</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Incentive Offers</t>
+          <t>Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Omni Hotels</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, Snowflake, PostgreSQL, MySQL, SQL, R, Java</t>
+          <t>RAG, CI/CD, Git, PySpark, MySQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,67 +916,67 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c447b651ee800dde</t>
+          <t>https://www.indeed.com/viewjob?jk=9e4e11c6fb2ec5b8</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DEVSECOPS(Openshift/Harness/Github Actions)</t>
+          <t>GCP Data Architect</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CI/CD, Jenkins, GitHub Actions, Git, Kafka, MongoDB, Python, SQL, R, Java</t>
+          <t>RAG, BigQuery, Dataflow, Git, BigQuery, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=533d36ca5b4598d9</t>
+          <t>https://www.indeed.com/viewjob?jk=3d68a9f74f5597a0</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr. Marketing Data Analyst</t>
+          <t>Snowflake Database Administrator / Developer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>WebstaurantStore</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Lititz, PA, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Data Lake, BigQuery, Tableau, Power BI, Python, SQL, R, Scala</t>
+          <t>RAG, CI/CD, Git, Snowflake, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffd7a5644f82136e</t>
+          <t>https://www.indeed.com/viewjob?jk=0b99c13e4176bd2a</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr. Business Intelligence Engineer</t>
+          <t>Software Engineer, Senior</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Crane Worldwide Logistics</t>
+          <t>Freddie Mac</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Power BI, Python, SQL</t>
+          <t>Data Scientist, S3, Docker, Jenkins, Git, PySpark, Python, R, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca7e276fb38eb9c1</t>
+          <t>https://www.indeed.com/viewjob?jk=a1c58592090c9820</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Infrastructure &amp; AI</t>
+          <t>Data Science Senior Associate - Card Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>fullstory</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Git, Snowflake, Databricks, BigQuery, Python, R, Java, Scala</t>
+          <t>RAG, Prompt Engineering, Git, Hadoop, Tableau, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,304 +1056,304 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6120c45b70e1da1f</t>
+          <t>https://www.indeed.com/viewjob?jk=947e08aebd96c2f0</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer - Moneylion</t>
+          <t>Senior AI Governance Scientist - Artificial Intelligence</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Gen Digital Inc.</t>
+          <t>Centene</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, PyTorch, MLflow, Databricks, Python, R</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72184d7f26e035eb</t>
+          <t>https://www.indeed.com/viewjob?jk=e0ce6333408da235</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer - Moneylion</t>
+          <t>Senior AI Governance Scientist - Artificial Intelligence</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Gen Digital Inc.</t>
+          <t>Centene</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, PyTorch, MLflow, Databricks, Python, R</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dafd0312251318c4</t>
+          <t>https://www.indeed.com/viewjob?jk=a98169697b5674a9</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Ops Engineer (contract)</t>
+          <t>Senior AI Governance Scientist - Artificial Intelligence</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Centene</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Prompt Engineering, BigQuery, Data Lake, BigQuery, PySpark, Kafka, Python, R</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, PyTorch, MLflow, Databricks, Python, R</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1e21d61725d3203</t>
+          <t>https://www.indeed.com/viewjob?jk=d5f349217eea52c3</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior AI Governance Scientist - Artificial Intelligence</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Epiq</t>
+          <t>Centene</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Docker, Kubernetes, Terraform, PostgreSQL, Python, SQL, R, Scala</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, PyTorch, MLflow, Databricks, Python, R</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2384b69265cb7bcf</t>
+          <t>https://www.indeed.com/viewjob?jk=5a68d3ff4bb9115e</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>IT AI Development Intern</t>
+          <t>Senior AI Governance Scientist - Artificial Intelligence</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Amphenol CIT</t>
+          <t>Centene</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Saint Augustine, FL, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Generative AI, Copilot, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Git, Python, R, Java</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, PyTorch, MLflow, Databricks, Python, R</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4304f11c3c46c971</t>
+          <t>https://www.indeed.com/viewjob?jk=3f0b48cb8137cf0d</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>Senior AI Governance Scientist - Artificial Intelligence</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ResultStack</t>
+          <t>Centene</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Data Scientist, Docker, CI/CD, Git, Tableau, Power BI, Python, SQL, R, Optimization</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, PyTorch, MLflow, Databricks, Python, R</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=383dabd5b047d81f</t>
+          <t>https://www.indeed.com/viewjob?jk=79224b2aa73747f3</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>Senior AI Governance Scientist - Artificial Intelligence</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ResultStack</t>
+          <t>Centene</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Data Scientist, Docker, CI/CD, Git, Tableau, Power BI, Python, SQL, R, Optimization</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, PyTorch, MLflow, Databricks, Python, R</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b52adf19e2ee5eb</t>
+          <t>https://www.indeed.com/viewjob?jk=8bbebad370a086a1</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>Senior AI Governance Scientist - Artificial Intelligence</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ResultStack</t>
+          <t>Centene</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Data Scientist, Docker, CI/CD, Git, Tableau, Power BI, Python, SQL, R, Optimization</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, PyTorch, MLflow, Databricks, Python, R</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a7add81c0661915</t>
+          <t>https://www.indeed.com/viewjob?jk=203ec6eb51ba25a2</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Developer - Information Governance</t>
+          <t>Senior AI Governance Scientist - Artificial Intelligence</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Epiq</t>
+          <t>Centene</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, GitHub Actions, Git, NoSQL, Power BI, SQL, R, Java</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, PyTorch, MLflow, Databricks, Python, R</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88087b3c950df52e</t>
+          <t>https://www.indeed.com/viewjob?jk=224d420efc64ac50</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Engineering</t>
+          <t>Senior AI Governance Scientist - Artificial Intelligence</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Chime</t>
+          <t>Centene</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RAG, Glue, Redshift, Snowflake, Redshift, Python, SQL, R, Scala</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, PyTorch, MLflow, Databricks, Python, R</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c132b6601f3c0c7</t>
+          <t>https://www.indeed.com/viewjob?jk=853a11d65ccd20f6</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AI Solutions Architect</t>
+          <t>Senior AI Governance Scientist - Artificial Intelligence</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>COLORADO SCHOOL OF MINES</t>
+          <t>Centene</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Gemini, Copilot, Prompt Engineering, Git, R</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, PyTorch, MLflow, Databricks, Python, R</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=642b8ac64c59f946</t>
+          <t>https://www.indeed.com/viewjob?jk=b505e715f63e173d</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Applied AI Engineer, Silicon Co-Design Group, New College Grad 2026</t>
+          <t>Senior AI Governance Scientist - Artificial Intelligence</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Centene</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,17 +1466,192 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, TensorFlow, PyTorch, CI/CD, Git, Python, R, Scala</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, PyTorch, MLflow, Databricks, Python, R</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3fa64adf9400cb4</t>
+          <t>https://www.indeed.com/viewjob?jk=70932f98da1fd04f</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Senior AI Governance Scientist - Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Centene</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, LLaMA, PyTorch, MLflow, Databricks, Python, R</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=565fc23a6a90f90f</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Senior AI Governance Scientist - Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Centene</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NC, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, LLaMA, PyTorch, MLflow, Databricks, Python, R</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c3188cb28419ebda</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Senior AI Governance Scientist - Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Centene</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>PA, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, LLaMA, PyTorch, MLflow, Databricks, Python, R</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2834c3040faa5f99</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Senior AI Governance Scientist - Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Centene</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, LLaMA, PyTorch, MLflow, Databricks, Python, R</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cd93475ebcbd228d</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer, ML Applications</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Rivian</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Kubernetes, CI/CD, Git, MongoDB, NoSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d7be056f4b15a426</t>
         </is>
       </c>
     </row>
